--- a/tests/archean/reaction_network.xlsx
+++ b/tests/archean/reaction_network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{837398C7-89EF-44AC-A09D-D86AD9C49721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AC9173C-9264-455B-AB0B-C6C14CCC10C3}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{837398C7-89EF-44AC-A09D-D86AD9C49721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC82E85A-B936-4431-B576-A2FA487A7ACF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="325">
   <si>
     <t>@format:idx</t>
   </si>
@@ -864,13 +864,161 @@
   </si>
   <si>
     <t>2.19d-10</t>
+  </si>
+  <si>
+    <t>CHOCHO</t>
+  </si>
+  <si>
+    <t>HCOOH</t>
+  </si>
+  <si>
+    <t>CH3CHO</t>
+  </si>
+  <si>
+    <t>CH3CO</t>
+  </si>
+  <si>
+    <t>CH3COOH</t>
+  </si>
+  <si>
+    <t>C2H6</t>
+  </si>
+  <si>
+    <t>C2H5</t>
+  </si>
+  <si>
+    <t>5.0d-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98d-14 </t>
+  </si>
+  <si>
+    <t>9.1d-1</t>
+  </si>
+  <si>
+    <t>2.15d-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57d-09 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04d-7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00d-11 </t>
+  </si>
+  <si>
+    <t>1.10d-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83d-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80d-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38d-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45d-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96d-13 </t>
+  </si>
+  <si>
+    <t>4.50d-11</t>
+  </si>
+  <si>
+    <t>3.63d-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00d-17 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50d-10 </t>
+  </si>
+  <si>
+    <t>3.30d-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15d-15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66d-16 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00d-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10d-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92d-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40d-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60d-11 </t>
+  </si>
+  <si>
+    <t>3.30d-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05d-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57d-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92d-17 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52d-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29d-10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11d-16 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67d-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99d-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01d-10 </t>
+  </si>
+  <si>
+    <t>6.7d-33</t>
+  </si>
+  <si>
+    <t>3.2d-30</t>
+  </si>
+  <si>
+    <t>COCOOH</t>
+  </si>
+  <si>
+    <t>2.99d-13*exp(-2586/T)</t>
+    <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <t>3.99d-11*exp(-2068.2/T)</t>
+  </si>
+  <si>
+    <t>2.62d-13*exp(-3010/T)</t>
+  </si>
+  <si>
+    <t>7.42d-11*(T/298)**(-0.69d0)*exp(-88.04/T)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,13 +1039,32 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -927,13 +1094,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -950,6 +1126,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1215,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:I269"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
@@ -3497,23 +3677,23 @@
         <v>174</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="2">
+    <row r="111" spans="1:8" s="5" customFormat="1">
+      <c r="A111" s="3">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F111" t="s">
-        <v>12</v>
-      </c>
-      <c r="H111" t="s">
+      <c r="F111" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H111" s="5" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5861,9 +6041,850 @@
         <v>181</v>
       </c>
     </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>24</v>
+      </c>
+      <c r="C228" t="s">
+        <v>24</v>
+      </c>
+      <c r="E228" t="s">
+        <v>276</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="2">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>276</v>
+      </c>
+      <c r="C229" t="s">
+        <v>12</v>
+      </c>
+      <c r="E229" t="s">
+        <v>25</v>
+      </c>
+      <c r="F229" t="s">
+        <v>42</v>
+      </c>
+      <c r="G229" t="s">
+        <v>24</v>
+      </c>
+      <c r="H229" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="2">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>276</v>
+      </c>
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" t="s">
+        <v>24</v>
+      </c>
+      <c r="F230" t="s">
+        <v>25</v>
+      </c>
+      <c r="G230" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" s="2">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>23</v>
+      </c>
+      <c r="C231" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" t="s">
+        <v>277</v>
+      </c>
+      <c r="F231" t="s">
+        <v>12</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" s="2">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>23</v>
+      </c>
+      <c r="C232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E232" t="s">
+        <v>22</v>
+      </c>
+      <c r="H232" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" s="2">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>22</v>
+      </c>
+      <c r="C233" t="s">
+        <v>42</v>
+      </c>
+      <c r="E233" t="s">
+        <v>51</v>
+      </c>
+      <c r="F233" t="s">
+        <v>12</v>
+      </c>
+      <c r="H233" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="2">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>18</v>
+      </c>
+      <c r="C234" t="s">
+        <v>22</v>
+      </c>
+      <c r="E234" t="s">
+        <v>51</v>
+      </c>
+      <c r="F234" t="s">
+        <v>19</v>
+      </c>
+      <c r="H234" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="2">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>19</v>
+      </c>
+      <c r="C235" t="s">
+        <v>24</v>
+      </c>
+      <c r="E235" t="s">
+        <v>278</v>
+      </c>
+      <c r="H235" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="2">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>278</v>
+      </c>
+      <c r="C236" t="s">
+        <v>12</v>
+      </c>
+      <c r="E236" t="s">
+        <v>279</v>
+      </c>
+      <c r="F236" t="s">
+        <v>42</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="2">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>278</v>
+      </c>
+      <c r="C237" t="s">
+        <v>12</v>
+      </c>
+      <c r="E237" t="s">
+        <v>25</v>
+      </c>
+      <c r="F237" t="s">
+        <v>42</v>
+      </c>
+      <c r="G237" t="s">
+        <v>19</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="2">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>278</v>
+      </c>
+      <c r="C238" t="s">
+        <v>12</v>
+      </c>
+      <c r="E238" t="s">
+        <v>18</v>
+      </c>
+      <c r="F238" t="s">
+        <v>24</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="2">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>278</v>
+      </c>
+      <c r="C239" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" t="s">
+        <v>279</v>
+      </c>
+      <c r="F239" t="s">
+        <v>11</v>
+      </c>
+      <c r="H239" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="2">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>278</v>
+      </c>
+      <c r="C240" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" t="s">
+        <v>277</v>
+      </c>
+      <c r="F240" t="s">
+        <v>19</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="2">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>278</v>
+      </c>
+      <c r="C241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" t="s">
+        <v>280</v>
+      </c>
+      <c r="F241" t="s">
+        <v>12</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="2">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>279</v>
+      </c>
+      <c r="C242" t="s">
+        <v>24</v>
+      </c>
+      <c r="E242" t="s">
+        <v>278</v>
+      </c>
+      <c r="F242" t="s">
+        <v>25</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="2">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>24</v>
+      </c>
+      <c r="C243" t="s">
+        <v>24</v>
+      </c>
+      <c r="E243" t="s">
+        <v>25</v>
+      </c>
+      <c r="F243" t="s">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>42</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="2">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>23</v>
+      </c>
+      <c r="C244" t="s">
+        <v>24</v>
+      </c>
+      <c r="E244" t="s">
+        <v>22</v>
+      </c>
+      <c r="F244" t="s">
+        <v>25</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="2">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>22</v>
+      </c>
+      <c r="C245" t="s">
+        <v>24</v>
+      </c>
+      <c r="E245" t="s">
+        <v>51</v>
+      </c>
+      <c r="F245" t="s">
+        <v>25</v>
+      </c>
+      <c r="H245" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="2">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>22</v>
+      </c>
+      <c r="C246" t="s">
+        <v>12</v>
+      </c>
+      <c r="E246" t="s">
+        <v>23</v>
+      </c>
+      <c r="F246" t="s">
+        <v>42</v>
+      </c>
+      <c r="H246" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" s="2">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>22</v>
+      </c>
+      <c r="C247" t="s">
+        <v>23</v>
+      </c>
+      <c r="E247" t="s">
+        <v>51</v>
+      </c>
+      <c r="F247" t="s">
+        <v>24</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" s="2">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>19</v>
+      </c>
+      <c r="C248" t="s">
+        <v>25</v>
+      </c>
+      <c r="E248" t="s">
+        <v>279</v>
+      </c>
+      <c r="H248" s="7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" s="2">
+        <v>249</v>
+      </c>
+      <c r="B249" t="s">
+        <v>19</v>
+      </c>
+      <c r="C249" t="s">
+        <v>23</v>
+      </c>
+      <c r="E249" t="s">
+        <v>18</v>
+      </c>
+      <c r="F249" t="s">
+        <v>24</v>
+      </c>
+      <c r="H249" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" s="2">
+        <v>250</v>
+      </c>
+      <c r="B250" t="s">
+        <v>19</v>
+      </c>
+      <c r="C250" t="s">
+        <v>19</v>
+      </c>
+      <c r="E250" t="s">
+        <v>281</v>
+      </c>
+      <c r="H250" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" s="2">
+        <v>251</v>
+      </c>
+      <c r="B251" t="s">
+        <v>279</v>
+      </c>
+      <c r="C251" t="s">
+        <v>4</v>
+      </c>
+      <c r="E251" t="s">
+        <v>23</v>
+      </c>
+      <c r="F251" t="s">
+        <v>24</v>
+      </c>
+      <c r="H251" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="2">
+        <v>252</v>
+      </c>
+      <c r="B252" t="s">
+        <v>279</v>
+      </c>
+      <c r="C252" t="s">
+        <v>12</v>
+      </c>
+      <c r="E252" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" t="s">
+        <v>24</v>
+      </c>
+      <c r="H252" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="2">
+        <v>253</v>
+      </c>
+      <c r="B253" t="s">
+        <v>279</v>
+      </c>
+      <c r="C253" t="s">
+        <v>12</v>
+      </c>
+      <c r="E253" t="s">
+        <v>252</v>
+      </c>
+      <c r="F253" t="s">
+        <v>42</v>
+      </c>
+      <c r="H253" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="2">
+        <v>254</v>
+      </c>
+      <c r="B254" t="s">
+        <v>279</v>
+      </c>
+      <c r="C254" t="s">
+        <v>19</v>
+      </c>
+      <c r="E254" t="s">
+        <v>281</v>
+      </c>
+      <c r="F254" t="s">
+        <v>25</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="2">
+        <v>255</v>
+      </c>
+      <c r="B255" t="s">
+        <v>279</v>
+      </c>
+      <c r="C255" t="s">
+        <v>19</v>
+      </c>
+      <c r="E255" t="s">
+        <v>252</v>
+      </c>
+      <c r="F255" t="s">
+        <v>18</v>
+      </c>
+      <c r="H255" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="2">
+        <v>256</v>
+      </c>
+      <c r="B256" t="s">
+        <v>252</v>
+      </c>
+      <c r="C256" t="s">
+        <v>4</v>
+      </c>
+      <c r="E256" t="s">
+        <v>23</v>
+      </c>
+      <c r="F256" t="s">
+        <v>25</v>
+      </c>
+      <c r="H256" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" s="2">
+        <v>257</v>
+      </c>
+      <c r="B257" t="s">
+        <v>252</v>
+      </c>
+      <c r="C257" t="s">
+        <v>12</v>
+      </c>
+      <c r="E257" t="s">
+        <v>19</v>
+      </c>
+      <c r="F257" t="s">
+        <v>25</v>
+      </c>
+      <c r="H257" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" s="2">
+        <v>258</v>
+      </c>
+      <c r="B258" t="s">
+        <v>278</v>
+      </c>
+      <c r="C258" t="s">
+        <v>4</v>
+      </c>
+      <c r="E258" t="s">
+        <v>279</v>
+      </c>
+      <c r="F258" t="s">
+        <v>9</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" s="2">
+        <v>259</v>
+      </c>
+      <c r="B259" t="s">
+        <v>281</v>
+      </c>
+      <c r="C259" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" t="s">
+        <v>282</v>
+      </c>
+      <c r="F259" t="s">
+        <v>42</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" s="2">
+        <v>260</v>
+      </c>
+      <c r="B260" t="s">
+        <v>281</v>
+      </c>
+      <c r="C260" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260" t="s">
+        <v>282</v>
+      </c>
+      <c r="F260" t="s">
+        <v>11</v>
+      </c>
+      <c r="H260" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" s="2">
+        <v>261</v>
+      </c>
+      <c r="B261" t="s">
+        <v>281</v>
+      </c>
+      <c r="C261" t="s">
+        <v>7</v>
+      </c>
+      <c r="E261" t="s">
+        <v>282</v>
+      </c>
+      <c r="F261" t="s">
+        <v>9</v>
+      </c>
+      <c r="H261" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" s="2">
+        <v>262</v>
+      </c>
+      <c r="B262" t="s">
+        <v>281</v>
+      </c>
+      <c r="C262" t="s">
+        <v>4</v>
+      </c>
+      <c r="E262" t="s">
+        <v>282</v>
+      </c>
+      <c r="F262" t="s">
+        <v>9</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" s="2">
+        <v>263</v>
+      </c>
+      <c r="B263" t="s">
+        <v>282</v>
+      </c>
+      <c r="C263" t="s">
+        <v>4</v>
+      </c>
+      <c r="E263" t="s">
+        <v>278</v>
+      </c>
+      <c r="F263" t="s">
+        <v>12</v>
+      </c>
+      <c r="H263" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" s="2">
+        <v>264</v>
+      </c>
+      <c r="B264" t="s">
+        <v>282</v>
+      </c>
+      <c r="C264" t="s">
+        <v>4</v>
+      </c>
+      <c r="E264" t="s">
+        <v>23</v>
+      </c>
+      <c r="F264" t="s">
+        <v>19</v>
+      </c>
+      <c r="H264" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" s="2">
+        <v>265</v>
+      </c>
+      <c r="B265" t="s">
+        <v>282</v>
+      </c>
+      <c r="C265" t="s">
+        <v>12</v>
+      </c>
+      <c r="E265" t="s">
+        <v>19</v>
+      </c>
+      <c r="F265" t="s">
+        <v>19</v>
+      </c>
+      <c r="H265" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" s="2">
+        <v>266</v>
+      </c>
+      <c r="B266" t="s">
+        <v>282</v>
+      </c>
+      <c r="C266" t="s">
+        <v>24</v>
+      </c>
+      <c r="E266" t="s">
+        <v>281</v>
+      </c>
+      <c r="F266" t="s">
+        <v>25</v>
+      </c>
+      <c r="H266" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" s="2">
+        <v>267</v>
+      </c>
+      <c r="B267" t="s">
+        <v>58</v>
+      </c>
+      <c r="C267" t="s">
+        <v>12</v>
+      </c>
+      <c r="D267" t="s">
+        <v>41</v>
+      </c>
+      <c r="E267" t="s">
+        <v>277</v>
+      </c>
+      <c r="F267" t="s">
+        <v>41</v>
+      </c>
+      <c r="H267" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="18">
+      <c r="A268" s="2">
+        <v>268</v>
+      </c>
+      <c r="B268" t="s">
+        <v>24</v>
+      </c>
+      <c r="C268" t="s">
+        <v>9</v>
+      </c>
+      <c r="D268" t="s">
+        <v>41</v>
+      </c>
+      <c r="E268" t="s">
+        <v>277</v>
+      </c>
+      <c r="F268" t="s">
+        <v>41</v>
+      </c>
+      <c r="H268" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="I268" s="6"/>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" s="2">
+        <v>269</v>
+      </c>
+      <c r="B269" t="s">
+        <v>58</v>
+      </c>
+      <c r="C269" t="s">
+        <v>25</v>
+      </c>
+      <c r="E269" t="s">
+        <v>320</v>
+      </c>
+      <c r="H269" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tests/archean/reaction_network.xlsx
+++ b/tests/archean/reaction_network.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{837398C7-89EF-44AC-A09D-D86AD9C49721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC82E85A-B936-4431-B576-A2FA487A7ACF}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{837398C7-89EF-44AC-A09D-D86AD9C49721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7613EBA2-9C7C-4D30-9C80-50637507386C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="326">
   <si>
     <t>@format:idx</t>
   </si>
@@ -1012,17 +1012,21 @@
   </si>
   <si>
     <t>7.42d-11*(T/298)**(-0.69d0)*exp(-88.04/T)</t>
+  </si>
+  <si>
+    <t>HCO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1034,7 +1038,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1042,7 +1046,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1126,10 +1130,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1396,13 +1396,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I269"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.5" thickBot="1">
+    <row r="1" spans="1:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -2175,12 +2175,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -2195,7 +2195,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="16" customHeight="1">
+    <row r="45" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="F85" t="s">
         <v>41</v>
@@ -3159,7 +3159,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E86" t="s">
         <v>42</v>
@@ -3179,15 +3179,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E87" t="s">
         <v>23</v>
@@ -3199,7 +3199,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -3219,7 +3219,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
@@ -3239,7 +3239,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -3259,7 +3259,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3273,13 +3273,13 @@
         <v>42</v>
       </c>
       <c r="F91" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H91" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -3293,13 +3293,13 @@
         <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H92" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="F102" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H102" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="111" spans="1:8" s="5" customFormat="1">
+    <row r="111" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -3863,12 +3863,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C120" t="s">
         <v>19</v>
@@ -3883,7 +3883,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>48</v>
       </c>
       <c r="E128" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="F128" t="s">
         <v>12</v>
@@ -4037,7 +4037,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -4203,12 +4203,12 @@
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A137" s="2">
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C137" t="s">
         <v>48</v>
@@ -4223,7 +4223,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="F141" t="s">
         <v>15</v>
@@ -4303,7 +4303,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -4317,13 +4317,13 @@
         <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H142" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E167" t="s">
         <v>51</v>
@@ -4820,7 +4820,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>47</v>
       </c>
       <c r="C168" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E168" t="s">
         <v>23</v>
@@ -4840,7 +4840,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A181" s="2">
         <v>180</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A183" s="2">
         <v>182</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A185" s="2">
         <v>184</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A187" s="2">
         <v>186</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A188" s="2">
         <v>187</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A189" s="2">
         <v>188</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A191" s="2">
         <v>190</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A193" s="2">
         <v>192</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A195" s="2">
         <v>194</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A199" s="2">
         <v>198</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A201" s="2">
         <v>200</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A203" s="2">
         <v>202</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A205" s="2">
         <v>204</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A207" s="2">
         <v>206</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A209" s="2">
         <v>208</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A211" s="2">
         <v>210</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A213" s="2">
         <v>212</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A219" s="2">
         <v>218</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A221" s="2">
         <v>220</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A223" s="2">
         <v>222</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A227" s="2">
         <v>226</v>
       </c>
@@ -6041,15 +6041,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A228" s="3">
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C228" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E228" t="s">
         <v>276</v>
@@ -6058,7 +6058,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" s="2">
         <v>228</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>9</v>
       </c>
       <c r="E230" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="F230" t="s">
         <v>25</v>
@@ -6104,7 +6104,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" s="2">
         <v>230</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" s="2">
         <v>232</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>19</v>
       </c>
       <c r="C235" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E235" t="s">
         <v>278</v>
@@ -6198,7 +6198,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" s="2">
         <v>236</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -6255,13 +6255,13 @@
         <v>18</v>
       </c>
       <c r="F238" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H238" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A239" s="2">
         <v>238</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>279</v>
       </c>
       <c r="C242" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E242" t="s">
         <v>278</v>
@@ -6341,15 +6341,15 @@
         <v>296</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A243" s="2">
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C243" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E243" t="s">
         <v>25</v>
@@ -6364,7 +6364,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E244" t="s">
         <v>22</v>
@@ -6384,7 +6384,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A245" s="2">
         <v>244</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>22</v>
       </c>
       <c r="C245" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E245" t="s">
         <v>51</v>
@@ -6404,7 +6404,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A247" s="2">
         <v>246</v>
       </c>
@@ -6438,13 +6438,13 @@
         <v>51</v>
       </c>
       <c r="F247" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -6475,13 +6475,13 @@
         <v>18</v>
       </c>
       <c r="F249" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -6512,13 +6512,13 @@
         <v>23</v>
       </c>
       <c r="F251" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -6532,13 +6532,13 @@
         <v>19</v>
       </c>
       <c r="F252" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="H252" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -6778,7 +6778,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>282</v>
       </c>
       <c r="C266" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E266" t="s">
         <v>281</v>
@@ -6818,7 +6818,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -6841,12 +6841,12 @@
         <v>318</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="18">
+    <row r="268" spans="1:9" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A268" s="2">
         <v>268</v>
       </c>
       <c r="B268" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="C268" t="s">
         <v>9</v>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="I268" s="6"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A269" s="2">
         <v>269</v>
       </c>

--- a/tests/archean/reaction_network.xlsx
+++ b/tests/archean/reaction_network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{837398C7-89EF-44AC-A09D-D86AD9C49721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7613EBA2-9C7C-4D30-9C80-50637507386C}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{837398C7-89EF-44AC-A09D-D86AD9C49721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152C7368-38D0-4CCF-8F7D-DCC4D3028C5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="325">
   <si>
     <t>@format:idx</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>CH2O</t>
-  </si>
-  <si>
-    <t>CHO</t>
   </si>
   <si>
     <t>CO</t>
@@ -1130,6 +1127,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1439,16 +1440,16 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -1468,7 +1469,7 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -1488,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -1511,7 +1512,7 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1531,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -1551,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -1571,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -1594,7 +1595,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1614,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -1634,7 +1635,7 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -1651,10 +1652,10 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -1671,7 +1672,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -1691,7 +1692,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -1711,7 +1712,7 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -1731,7 +1732,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -1751,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -1771,7 +1772,7 @@
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -1785,16 +1786,16 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" t="s">
         <v>81</v>
-      </c>
-      <c r="F19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -1808,16 +1809,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1831,7 +1832,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -1840,10 +1841,10 @@
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -1863,7 +1864,7 @@
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -1883,7 +1884,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -1903,7 +1904,7 @@
         <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -1917,16 +1918,16 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -1946,7 +1947,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -1966,7 +1967,7 @@
         <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -1986,7 +1987,7 @@
         <v>11</v>
       </c>
       <c r="H28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -2000,13 +2001,13 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -2026,7 +2027,7 @@
         <v>11</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -2040,16 +2041,16 @@
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -2069,7 +2070,7 @@
         <v>5</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -2089,7 +2090,7 @@
         <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
@@ -2112,7 +2113,7 @@
         <v>11</v>
       </c>
       <c r="H34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -2132,7 +2133,7 @@
         <v>11</v>
       </c>
       <c r="H35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
@@ -2152,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -2166,13 +2167,13 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="H37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -2180,19 +2181,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
@@ -2200,25 +2201,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
@@ -2232,19 +2233,19 @@
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
       </c>
       <c r="G40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
@@ -2252,7 +2253,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -2264,7 +2265,7 @@
         <v>11</v>
       </c>
       <c r="H41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
@@ -2272,19 +2273,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
@@ -2292,19 +2293,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
@@ -2312,19 +2313,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -2332,19 +2333,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
@@ -2352,19 +2353,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F46" t="s">
         <v>4</v>
       </c>
       <c r="H46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
@@ -2372,19 +2373,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
       </c>
       <c r="H47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
@@ -2392,19 +2393,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -2412,7 +2413,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -2421,10 +2422,10 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
@@ -2432,7 +2433,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -2441,10 +2442,10 @@
         <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
@@ -2452,19 +2453,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" t="s">
         <v>30</v>
       </c>
-      <c r="C51" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" t="s">
-        <v>31</v>
-      </c>
       <c r="H51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
@@ -2472,7 +2473,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -2481,10 +2482,10 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
@@ -2492,7 +2493,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
@@ -2501,10 +2502,10 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
@@ -2512,7 +2513,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -2521,10 +2522,10 @@
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
@@ -2532,19 +2533,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F55" t="s">
         <v>5</v>
       </c>
       <c r="H55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
@@ -2552,19 +2553,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
@@ -2572,19 +2573,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
         <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F57" t="s">
         <v>5</v>
       </c>
       <c r="H57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
@@ -2592,19 +2593,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
         <v>4</v>
       </c>
       <c r="H58" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
@@ -2612,19 +2613,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="H59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
@@ -2632,19 +2633,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
@@ -2652,19 +2653,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F61" t="s">
         <v>4</v>
       </c>
       <c r="H61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
@@ -2672,7 +2673,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
         <v>6</v>
@@ -2681,10 +2682,10 @@
         <v>5</v>
       </c>
       <c r="F62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
@@ -2692,7 +2693,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
         <v>9</v>
@@ -2701,10 +2702,10 @@
         <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
@@ -2712,7 +2713,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C64" t="s">
         <v>10</v>
@@ -2721,10 +2722,10 @@
         <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
@@ -2732,19 +2733,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F65" t="s">
         <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.4">
@@ -2752,19 +2753,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C66" t="s">
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F66" t="s">
         <v>5</v>
       </c>
       <c r="H66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
@@ -2772,19 +2773,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
       </c>
       <c r="H67" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.4">
@@ -2792,7 +2793,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
         <v>6</v>
@@ -2804,10 +2805,10 @@
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">
@@ -2815,7 +2816,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -2824,10 +2825,10 @@
         <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.4">
@@ -2835,7 +2836,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -2844,10 +2845,10 @@
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.4">
@@ -2855,7 +2856,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -2864,10 +2865,10 @@
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.4">
@@ -2875,16 +2876,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.4">
@@ -2892,22 +2893,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C73" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E73" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.4">
@@ -2915,22 +2916,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H74" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.4">
@@ -2938,16 +2939,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.4">
@@ -2955,16 +2956,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C76" t="s">
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H76" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.4">
@@ -2972,25 +2973,25 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C77" t="s">
         <v>9</v>
       </c>
       <c r="D77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F77" t="s">
+        <v>139</v>
+      </c>
+      <c r="G77" t="s">
+        <v>40</v>
+      </c>
+      <c r="H77" t="s">
         <v>140</v>
-      </c>
-      <c r="G77" t="s">
-        <v>41</v>
-      </c>
-      <c r="H77" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.4">
@@ -2998,13 +2999,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E78" t="s">
+        <v>141</v>
+      </c>
+      <c r="H78" t="s">
         <v>142</v>
-      </c>
-      <c r="H78" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.4">
@@ -3024,7 +3025,7 @@
         <v>9</v>
       </c>
       <c r="H79" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
@@ -3044,7 +3045,7 @@
         <v>12</v>
       </c>
       <c r="H80" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.4">
@@ -3061,10 +3062,10 @@
         <v>23</v>
       </c>
       <c r="F81" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.4">
@@ -3087,7 +3088,7 @@
         <v>5</v>
       </c>
       <c r="H82" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.4">
@@ -3101,7 +3102,7 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -3110,7 +3111,7 @@
         <v>5</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -3121,19 +3122,19 @@
         <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H84" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
@@ -3144,19 +3145,19 @@
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E85" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.4">
@@ -3167,16 +3168,16 @@
         <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H86" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.4">
@@ -3184,19 +3185,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C87" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E87" t="s">
         <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H87" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.4">
@@ -3207,16 +3208,16 @@
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H88" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -3227,16 +3228,16 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H89" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.4">
@@ -3247,16 +3248,16 @@
         <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H90" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.4">
@@ -3270,13 +3271,13 @@
         <v>23</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F91" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H91" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.4">
@@ -3293,10 +3294,10 @@
         <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.4">
@@ -3307,7 +3308,7 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
@@ -3316,7 +3317,7 @@
         <v>9</v>
       </c>
       <c r="H93" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.4">
@@ -3327,7 +3328,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
@@ -3336,7 +3337,7 @@
         <v>11</v>
       </c>
       <c r="H94" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.4">
@@ -3344,19 +3345,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
       </c>
       <c r="H95" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
@@ -3364,22 +3365,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H96" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
@@ -3387,19 +3388,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F97" t="s">
+        <v>159</v>
+      </c>
+      <c r="H97" t="s">
         <v>160</v>
-      </c>
-      <c r="H97" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
@@ -3407,19 +3408,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" t="s">
+        <v>31</v>
+      </c>
+      <c r="E98" t="s">
         <v>32</v>
       </c>
-      <c r="C98" t="s">
-        <v>32</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>33</v>
       </c>
-      <c r="F98" t="s">
-        <v>34</v>
-      </c>
       <c r="H98" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
@@ -3427,19 +3428,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H99" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -3447,19 +3448,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H100" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
@@ -3467,19 +3468,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H101" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
@@ -3487,19 +3488,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="E102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H102" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
@@ -3507,22 +3508,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E103" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H103" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.4">
@@ -3530,22 +3531,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104" t="s">
+        <v>40</v>
+      </c>
+      <c r="E104" t="s">
         <v>44</v>
       </c>
-      <c r="D104" t="s">
-        <v>41</v>
-      </c>
-      <c r="E104" t="s">
-        <v>45</v>
-      </c>
       <c r="F104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H104" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
@@ -3553,22 +3554,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" t="s">
+        <v>40</v>
+      </c>
+      <c r="E105" t="s">
         <v>45</v>
       </c>
-      <c r="D105" t="s">
-        <v>41</v>
-      </c>
-      <c r="E105" t="s">
-        <v>46</v>
-      </c>
       <c r="F105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H105" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
@@ -3576,22 +3577,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D106" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E106" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F106" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H106" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
@@ -3599,22 +3600,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C107" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D107" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E107" t="s">
+        <v>169</v>
+      </c>
+      <c r="F107" t="s">
+        <v>40</v>
+      </c>
+      <c r="H107" t="s">
         <v>170</v>
-      </c>
-      <c r="F107" t="s">
-        <v>41</v>
-      </c>
-      <c r="H107" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -3622,22 +3623,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C108" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G108" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H108" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.4">
@@ -3645,19 +3646,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C109" t="s">
         <v>4</v>
       </c>
       <c r="E109" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H109" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -3674,7 +3675,7 @@
         <v>22</v>
       </c>
       <c r="H110" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -3694,7 +3695,7 @@
         <v>12</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
@@ -3708,16 +3709,16 @@
         <v>19</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E112" t="s">
         <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.4">
@@ -3737,7 +3738,7 @@
         <v>5</v>
       </c>
       <c r="H113" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
@@ -3745,7 +3746,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C114" t="s">
         <v>19</v>
@@ -3757,7 +3758,7 @@
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
@@ -3777,7 +3778,7 @@
         <v>12</v>
       </c>
       <c r="H115" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
@@ -3797,7 +3798,7 @@
         <v>4</v>
       </c>
       <c r="H116" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.4">
@@ -3811,16 +3812,16 @@
         <v>19</v>
       </c>
       <c r="D117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E117" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H117" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
@@ -3840,7 +3841,7 @@
         <v>9</v>
       </c>
       <c r="H118" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
@@ -3860,7 +3861,7 @@
         <v>5</v>
       </c>
       <c r="H119" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
@@ -3868,7 +3869,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C120" t="s">
         <v>19</v>
@@ -3877,10 +3878,10 @@
         <v>18</v>
       </c>
       <c r="F120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H120" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
@@ -3897,10 +3898,10 @@
         <v>18</v>
       </c>
       <c r="F121" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H121" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
@@ -3914,10 +3915,10 @@
         <v>12</v>
       </c>
       <c r="F122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H122" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
@@ -3928,13 +3929,13 @@
         <v>19</v>
       </c>
       <c r="E123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H123" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
@@ -3954,7 +3955,7 @@
         <v>18</v>
       </c>
       <c r="H124" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
@@ -3962,7 +3963,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C125" t="s">
         <v>19</v>
@@ -3974,7 +3975,7 @@
         <v>18</v>
       </c>
       <c r="H125" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
@@ -3994,7 +3995,7 @@
         <v>22</v>
       </c>
       <c r="H126" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -4002,7 +4003,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
@@ -4014,7 +4015,7 @@
         <v>12</v>
       </c>
       <c r="H127" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -4025,16 +4026,16 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E128" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F128" t="s">
         <v>12</v>
       </c>
       <c r="H128" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
@@ -4045,7 +4046,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E129" t="s">
         <v>12</v>
@@ -4054,10 +4055,10 @@
         <v>12</v>
       </c>
       <c r="G129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H129" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -4068,16 +4069,16 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H130" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -4088,16 +4089,16 @@
         <v>12</v>
       </c>
       <c r="C131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F131" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H131" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -4108,19 +4109,19 @@
         <v>5</v>
       </c>
       <c r="C132" t="s">
+        <v>47</v>
+      </c>
+      <c r="E132" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" t="s">
+        <v>12</v>
+      </c>
+      <c r="G132" t="s">
         <v>48</v>
       </c>
-      <c r="E132" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" t="s">
-        <v>12</v>
-      </c>
-      <c r="G132" t="s">
-        <v>49</v>
-      </c>
       <c r="H132" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -4131,16 +4132,16 @@
         <v>5</v>
       </c>
       <c r="C133" t="s">
+        <v>47</v>
+      </c>
+      <c r="E133" t="s">
+        <v>41</v>
+      </c>
+      <c r="F133" t="s">
         <v>48</v>
       </c>
-      <c r="E133" t="s">
-        <v>42</v>
-      </c>
-      <c r="F133" t="s">
-        <v>49</v>
-      </c>
       <c r="H133" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -4151,16 +4152,16 @@
         <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
       </c>
       <c r="H134" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -4171,7 +4172,7 @@
         <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E135" t="s">
         <v>4</v>
@@ -4180,7 +4181,7 @@
         <v>23</v>
       </c>
       <c r="H135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -4191,7 +4192,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E136" t="s">
         <v>12</v>
@@ -4200,7 +4201,7 @@
         <v>23</v>
       </c>
       <c r="H136" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -4208,19 +4209,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C137" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F137" t="s">
         <v>19</v>
       </c>
       <c r="H137" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -4231,7 +4232,7 @@
         <v>20</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E138" t="s">
         <v>23</v>
@@ -4240,7 +4241,7 @@
         <v>22</v>
       </c>
       <c r="H138" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -4248,19 +4249,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E139" t="s">
         <v>23</v>
       </c>
       <c r="F139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H139" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -4271,16 +4272,16 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E140" t="s">
         <v>12</v>
       </c>
       <c r="F140" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H140" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
@@ -4288,19 +4289,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
@@ -4311,16 +4312,16 @@
         <v>5</v>
       </c>
       <c r="C142" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E142" t="s">
         <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H142" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -4331,16 +4332,16 @@
         <v>5</v>
       </c>
       <c r="C143" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
       </c>
       <c r="F143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H143" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -4351,7 +4352,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E144" t="s">
         <v>12</v>
@@ -4360,7 +4361,7 @@
         <v>23</v>
       </c>
       <c r="H144" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -4368,19 +4369,19 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C145" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E145" t="s">
         <v>12</v>
       </c>
       <c r="F145" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H145" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.4">
@@ -4388,16 +4389,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C146" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
       </c>
       <c r="H146" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.4">
@@ -4405,10 +4406,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C147" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E147" t="s">
         <v>22</v>
@@ -4417,7 +4418,7 @@
         <v>19</v>
       </c>
       <c r="H147" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.4">
@@ -4425,19 +4426,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C148" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E148" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F148" t="s">
         <v>19</v>
       </c>
       <c r="H148" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.4">
@@ -4445,7 +4446,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C149" t="s">
         <v>4</v>
@@ -4457,7 +4458,7 @@
         <v>9</v>
       </c>
       <c r="H149" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -4465,19 +4466,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C150" t="s">
         <v>4</v>
       </c>
       <c r="E150" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F150" t="s">
         <v>9</v>
       </c>
       <c r="H150" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -4485,7 +4486,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C151" t="s">
         <v>12</v>
@@ -4497,7 +4498,7 @@
         <v>11</v>
       </c>
       <c r="H151" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -4505,7 +4506,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C152" t="s">
         <v>12</v>
@@ -4514,10 +4515,10 @@
         <v>22</v>
       </c>
       <c r="F152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H152" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -4525,19 +4526,19 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C153" t="s">
         <v>12</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H153" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -4545,7 +4546,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C154" t="s">
         <v>9</v>
@@ -4557,7 +4558,7 @@
         <v>11</v>
       </c>
       <c r="H154" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -4565,19 +4566,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C155" t="s">
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F155" t="s">
         <v>11</v>
       </c>
       <c r="H155" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -4585,7 +4586,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C156" t="s">
         <v>9</v>
@@ -4600,7 +4601,7 @@
         <v>12</v>
       </c>
       <c r="H156" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -4608,7 +4609,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C157" t="s">
         <v>19</v>
@@ -4620,7 +4621,7 @@
         <v>22</v>
       </c>
       <c r="H157" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -4628,7 +4629,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C158" t="s">
         <v>19</v>
@@ -4637,10 +4638,10 @@
         <v>18</v>
       </c>
       <c r="F158" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H158" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -4648,10 +4649,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>46</v>
+      </c>
+      <c r="C159" t="s">
         <v>47</v>
-      </c>
-      <c r="C159" t="s">
-        <v>48</v>
       </c>
       <c r="E159" t="s">
         <v>23</v>
@@ -4660,7 +4661,7 @@
         <v>19</v>
       </c>
       <c r="H159" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -4668,7 +4669,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C160" t="s">
         <v>4</v>
@@ -4680,7 +4681,7 @@
         <v>9</v>
       </c>
       <c r="H160" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -4688,7 +4689,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C161" t="s">
         <v>12</v>
@@ -4700,7 +4701,7 @@
         <v>9</v>
       </c>
       <c r="H161" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -4708,16 +4709,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C162" t="s">
         <v>12</v>
       </c>
       <c r="E162" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H162" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -4725,7 +4726,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C163" t="s">
         <v>12</v>
@@ -4734,10 +4735,10 @@
         <v>23</v>
       </c>
       <c r="F163" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H163" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -4745,19 +4746,19 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E164" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F164" t="s">
         <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -4765,7 +4766,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C165" t="s">
         <v>9</v>
@@ -4777,7 +4778,7 @@
         <v>11</v>
       </c>
       <c r="H165" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -4785,7 +4786,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C166" t="s">
         <v>10</v>
@@ -4794,10 +4795,10 @@
         <v>23</v>
       </c>
       <c r="F166" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H166" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -4805,19 +4806,19 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C167" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E167" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F167" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H167" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -4825,10 +4826,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E168" t="s">
         <v>23</v>
@@ -4837,7 +4838,7 @@
         <v>23</v>
       </c>
       <c r="H168" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -4845,19 +4846,19 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E169" t="s">
         <v>23</v>
       </c>
       <c r="F169" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H169" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -4865,7 +4866,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -4877,7 +4878,7 @@
         <v>15</v>
       </c>
       <c r="H170" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -4885,7 +4886,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C171" t="s">
         <v>15</v>
@@ -4897,7 +4898,7 @@
         <v>4</v>
       </c>
       <c r="H171" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -4917,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="H172" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -4937,7 +4938,7 @@
         <v>14</v>
       </c>
       <c r="H173" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -4945,22 +4946,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>52</v>
+      </c>
+      <c r="C174" t="s">
+        <v>52</v>
+      </c>
+      <c r="D174" t="s">
+        <v>40</v>
+      </c>
+      <c r="E174" t="s">
         <v>53</v>
       </c>
-      <c r="C174" t="s">
-        <v>53</v>
-      </c>
-      <c r="D174" t="s">
-        <v>41</v>
-      </c>
-      <c r="E174" t="s">
-        <v>54</v>
-      </c>
       <c r="F174" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H174" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -4968,19 +4969,19 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>53</v>
+      </c>
+      <c r="C175" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175" t="s">
         <v>54</v>
       </c>
-      <c r="C175" t="s">
-        <v>12</v>
-      </c>
-      <c r="E175" t="s">
-        <v>55</v>
-      </c>
       <c r="F175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H175" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -4988,19 +4989,19 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C176" t="s">
         <v>12</v>
       </c>
       <c r="E176" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F176" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H176" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -5008,7 +5009,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C177" t="s">
         <v>15</v>
@@ -5020,7 +5021,7 @@
         <v>9</v>
       </c>
       <c r="H177" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -5028,19 +5029,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C178" t="s">
         <v>4</v>
       </c>
       <c r="E178" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F178" t="s">
         <v>9</v>
       </c>
       <c r="H178" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -5048,7 +5049,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C179" t="s">
         <v>15</v>
@@ -5060,7 +5061,7 @@
         <v>11</v>
       </c>
       <c r="H179" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -5068,19 +5069,19 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C180" t="s">
         <v>4</v>
       </c>
       <c r="E180" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F180" t="s">
         <v>9</v>
       </c>
       <c r="H180" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">
@@ -5088,19 +5089,19 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C181" t="s">
         <v>7</v>
       </c>
       <c r="E181" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F181" t="s">
         <v>9</v>
       </c>
       <c r="H181" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.4">
@@ -5108,19 +5109,19 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C182" t="s">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F182" t="s">
         <v>11</v>
       </c>
       <c r="H182" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.4">
@@ -5128,22 +5129,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C183" t="s">
         <v>12</v>
       </c>
       <c r="D183" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E183" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F183" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H183" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.4">
@@ -5151,7 +5152,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C184" t="s">
         <v>15</v>
@@ -5163,7 +5164,7 @@
         <v>12</v>
       </c>
       <c r="H184" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.4">
@@ -5171,7 +5172,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C185" t="s">
         <v>4</v>
@@ -5183,7 +5184,7 @@
         <v>12</v>
       </c>
       <c r="H185" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.4">
@@ -5194,16 +5195,16 @@
         <v>19</v>
       </c>
       <c r="C186" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E186" t="s">
         <v>18</v>
       </c>
       <c r="F186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H186" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.4">
@@ -5211,19 +5212,19 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C187" t="s">
         <v>12</v>
       </c>
       <c r="E187" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H187" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.4">
@@ -5231,19 +5232,19 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C188" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E188" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F188" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H188" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.4">
@@ -5251,19 +5252,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C189" t="s">
         <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F189" t="s">
         <v>15</v>
       </c>
       <c r="H189" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.4">
@@ -5271,19 +5272,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E190" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F190" t="s">
         <v>12</v>
       </c>
       <c r="H190" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.4">
@@ -5291,19 +5292,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C191" t="s">
         <v>4</v>
       </c>
       <c r="E191" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F191" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H191" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.4">
@@ -5311,19 +5312,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C192" t="s">
         <v>4</v>
       </c>
       <c r="E192" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F192" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H192" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.4">
@@ -5334,16 +5335,16 @@
         <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E193" t="s">
         <v>11</v>
       </c>
       <c r="F193" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H193" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.4">
@@ -5351,19 +5352,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E194" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F194" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H194" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.4">
@@ -5371,19 +5372,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C195" t="s">
+        <v>55</v>
+      </c>
+      <c r="E195" t="s">
         <v>56</v>
       </c>
-      <c r="E195" t="s">
-        <v>57</v>
-      </c>
       <c r="F195" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H195" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.4">
@@ -5394,19 +5395,19 @@
         <v>4</v>
       </c>
       <c r="C196" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E196" t="s">
         <v>15</v>
       </c>
       <c r="F196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H196" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.4">
@@ -5417,19 +5418,19 @@
         <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D197" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E197" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F197" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H197" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.4">
@@ -5440,7 +5441,7 @@
         <v>14</v>
       </c>
       <c r="C198" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E198" t="s">
         <v>13</v>
@@ -5449,7 +5450,7 @@
         <v>4</v>
       </c>
       <c r="H198" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.4">
@@ -5463,16 +5464,16 @@
         <v>4</v>
       </c>
       <c r="D199" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E199" t="s">
         <v>5</v>
       </c>
       <c r="F199" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H199" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.4">
@@ -5483,19 +5484,19 @@
         <v>9</v>
       </c>
       <c r="C200" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D200" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E200" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F200" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H200" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.4">
@@ -5503,19 +5504,19 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
+        <v>57</v>
+      </c>
+      <c r="C201" t="s">
         <v>58</v>
       </c>
-      <c r="C201" t="s">
-        <v>59</v>
-      </c>
       <c r="E201" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F201" t="s">
         <v>9</v>
       </c>
       <c r="H201" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.4">
@@ -5523,19 +5524,19 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C202" t="s">
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F202" t="s">
         <v>11</v>
       </c>
       <c r="H202" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.4">
@@ -5543,7 +5544,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C203" t="s">
         <v>19</v>
@@ -5552,10 +5553,10 @@
         <v>11</v>
       </c>
       <c r="F203" t="s">
+        <v>251</v>
+      </c>
+      <c r="H203" t="s">
         <v>252</v>
-      </c>
-      <c r="H203" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.4">
@@ -5563,7 +5564,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C204" t="s">
         <v>19</v>
@@ -5572,10 +5573,10 @@
         <v>18</v>
       </c>
       <c r="F204" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H204" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.4">
@@ -5583,7 +5584,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C205" t="s">
         <v>12</v>
@@ -5592,10 +5593,10 @@
         <v>11</v>
       </c>
       <c r="F205" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H205" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.4">
@@ -5603,19 +5604,19 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C206" t="s">
         <v>12</v>
       </c>
       <c r="E206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F206" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H206" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.4">
@@ -5629,16 +5630,16 @@
         <v>9</v>
       </c>
       <c r="D207" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E207" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F207" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H207" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.4">
@@ -5649,16 +5650,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E208" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F208" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H208" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.4">
@@ -5672,13 +5673,13 @@
         <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F209" t="s">
         <v>8</v>
       </c>
       <c r="H209" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.4">
@@ -5689,16 +5690,16 @@
         <v>7</v>
       </c>
       <c r="C210" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E210" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F210" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H210" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.4">
@@ -5709,7 +5710,7 @@
         <v>18</v>
       </c>
       <c r="C211" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E211" t="s">
         <v>19</v>
@@ -5718,7 +5719,7 @@
         <v>19</v>
       </c>
       <c r="H211" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.4">
@@ -5729,7 +5730,7 @@
         <v>4</v>
       </c>
       <c r="C212" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E212" t="s">
         <v>9</v>
@@ -5738,7 +5739,7 @@
         <v>12</v>
       </c>
       <c r="H212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.4">
@@ -5752,10 +5753,10 @@
         <v>12</v>
       </c>
       <c r="E213" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.4">
@@ -5763,7 +5764,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
@@ -5772,10 +5773,10 @@
         <v>10</v>
       </c>
       <c r="F214" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H214" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.4">
@@ -5783,19 +5784,19 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
       </c>
       <c r="E215" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F215" t="s">
         <v>19</v>
       </c>
       <c r="H215" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.4">
@@ -5806,19 +5807,19 @@
         <v>18</v>
       </c>
       <c r="C216" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E216" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F216" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G216" t="s">
         <v>12</v>
       </c>
       <c r="H216" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.4">
@@ -5829,16 +5830,16 @@
         <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E217" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F217" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H217" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.4">
@@ -5846,19 +5847,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C218" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E218" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F218" t="s">
         <v>12</v>
       </c>
       <c r="H218" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.4">
@@ -5869,10 +5870,10 @@
         <v>19</v>
       </c>
       <c r="C219" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E219" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F219" t="s">
         <v>12</v>
@@ -5881,7 +5882,7 @@
         <v>12</v>
       </c>
       <c r="H219" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.4">
@@ -5889,19 +5890,19 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C220" t="s">
         <v>9</v>
       </c>
       <c r="E220" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F220" t="s">
         <v>11</v>
       </c>
       <c r="H220" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.4">
@@ -5909,19 +5910,19 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C221" t="s">
         <v>4</v>
       </c>
       <c r="E221" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F221" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H221" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.4">
@@ -5929,16 +5930,16 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C222" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E222" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H222" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.4">
@@ -5946,19 +5947,19 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C223" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E223" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F223" t="s">
         <v>19</v>
       </c>
       <c r="H223" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.4">
@@ -5966,19 +5967,19 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C224" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E224" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F224" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H224" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.4">
@@ -5986,19 +5987,19 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
+        <v>62</v>
+      </c>
+      <c r="C225" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" t="s">
         <v>63</v>
-      </c>
-      <c r="C225" t="s">
-        <v>9</v>
-      </c>
-      <c r="E225" t="s">
-        <v>64</v>
       </c>
       <c r="F225" t="s">
         <v>11</v>
       </c>
       <c r="H225" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.4">
@@ -6006,19 +6007,19 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
+        <v>59</v>
+      </c>
+      <c r="C226" t="s">
+        <v>62</v>
+      </c>
+      <c r="E226" t="s">
         <v>60</v>
       </c>
-      <c r="C226" t="s">
+      <c r="F226" t="s">
         <v>63</v>
       </c>
-      <c r="E226" t="s">
-        <v>61</v>
-      </c>
-      <c r="F226" t="s">
-        <v>64</v>
-      </c>
       <c r="H226" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.4">
@@ -6026,19 +6027,19 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C227" t="s">
         <v>11</v>
       </c>
       <c r="E227" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F227" t="s">
         <v>5</v>
       </c>
       <c r="H227" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.4">
@@ -6046,16 +6047,16 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C228" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E228" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
@@ -6063,22 +6064,22 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C229" t="s">
         <v>12</v>
       </c>
       <c r="E229" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F229" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G229" t="s">
-        <v>24</v>
+        <v>324</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.4">
@@ -6086,22 +6087,22 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C230" t="s">
         <v>9</v>
       </c>
       <c r="E230" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F230" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G230" t="s">
         <v>11</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.4">
@@ -6115,13 +6116,13 @@
         <v>9</v>
       </c>
       <c r="E231" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F231" t="s">
         <v>12</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.4">
@@ -6138,7 +6139,7 @@
         <v>22</v>
       </c>
       <c r="H232" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.4">
@@ -6149,16 +6150,16 @@
         <v>22</v>
       </c>
       <c r="C233" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E233" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F233" t="s">
         <v>12</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.4">
@@ -6172,13 +6173,13 @@
         <v>22</v>
       </c>
       <c r="E234" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F234" t="s">
         <v>19</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.4">
@@ -6189,13 +6190,13 @@
         <v>19</v>
       </c>
       <c r="C235" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E235" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
@@ -6203,19 +6204,19 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
+        <v>277</v>
+      </c>
+      <c r="C236" t="s">
+        <v>12</v>
+      </c>
+      <c r="E236" t="s">
         <v>278</v>
       </c>
-      <c r="C236" t="s">
-        <v>12</v>
-      </c>
-      <c r="E236" t="s">
-        <v>279</v>
-      </c>
       <c r="F236" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
@@ -6223,22 +6224,22 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C237" t="s">
         <v>12</v>
       </c>
       <c r="E237" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F237" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G237" t="s">
         <v>19</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.4">
@@ -6246,7 +6247,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C238" t="s">
         <v>12</v>
@@ -6255,10 +6256,10 @@
         <v>18</v>
       </c>
       <c r="F238" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.4">
@@ -6266,19 +6267,19 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
+        <v>277</v>
+      </c>
+      <c r="C239" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" t="s">
         <v>278</v>
-      </c>
-      <c r="C239" t="s">
-        <v>9</v>
-      </c>
-      <c r="E239" t="s">
-        <v>279</v>
       </c>
       <c r="F239" t="s">
         <v>11</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.4">
@@ -6286,19 +6287,19 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C240" t="s">
         <v>9</v>
       </c>
       <c r="E240" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F240" t="s">
         <v>19</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.4">
@@ -6306,19 +6307,19 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C241" t="s">
         <v>9</v>
       </c>
       <c r="E241" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F241" t="s">
         <v>12</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.4">
@@ -6326,19 +6327,19 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C242" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E242" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F242" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.4">
@@ -6346,22 +6347,22 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C243" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E243" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F243" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G243" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.4">
@@ -6372,16 +6373,16 @@
         <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E244" t="s">
         <v>22</v>
       </c>
       <c r="F244" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.4">
@@ -6392,16 +6393,16 @@
         <v>22</v>
       </c>
       <c r="C245" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E245" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F245" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.4">
@@ -6418,10 +6419,10 @@
         <v>23</v>
       </c>
       <c r="F246" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.4">
@@ -6435,13 +6436,13 @@
         <v>23</v>
       </c>
       <c r="E247" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F247" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.4">
@@ -6452,13 +6453,13 @@
         <v>19</v>
       </c>
       <c r="C248" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E248" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H248" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.4">
@@ -6475,10 +6476,10 @@
         <v>18</v>
       </c>
       <c r="F249" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.4">
@@ -6492,10 +6493,10 @@
         <v>19</v>
       </c>
       <c r="E250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H250" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.4">
@@ -6503,7 +6504,7 @@
         <v>251</v>
       </c>
       <c r="B251" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C251" t="s">
         <v>4</v>
@@ -6512,10 +6513,10 @@
         <v>23</v>
       </c>
       <c r="F251" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.4">
@@ -6523,7 +6524,7 @@
         <v>252</v>
       </c>
       <c r="B252" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C252" t="s">
         <v>12</v>
@@ -6532,10 +6533,10 @@
         <v>19</v>
       </c>
       <c r="F252" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.4">
@@ -6543,19 +6544,19 @@
         <v>253</v>
       </c>
       <c r="B253" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C253" t="s">
         <v>12</v>
       </c>
       <c r="E253" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F253" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.4">
@@ -6563,19 +6564,19 @@
         <v>254</v>
       </c>
       <c r="B254" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C254" t="s">
         <v>19</v>
       </c>
       <c r="E254" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F254" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.4">
@@ -6583,19 +6584,19 @@
         <v>255</v>
       </c>
       <c r="B255" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C255" t="s">
         <v>19</v>
       </c>
       <c r="E255" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F255" t="s">
         <v>18</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.4">
@@ -6603,7 +6604,7 @@
         <v>256</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C256" t="s">
         <v>4</v>
@@ -6612,10 +6613,10 @@
         <v>23</v>
       </c>
       <c r="F256" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.4">
@@ -6623,7 +6624,7 @@
         <v>257</v>
       </c>
       <c r="B257" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C257" t="s">
         <v>12</v>
@@ -6632,10 +6633,10 @@
         <v>19</v>
       </c>
       <c r="F257" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.4">
@@ -6643,19 +6644,19 @@
         <v>258</v>
       </c>
       <c r="B258" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C258" t="s">
         <v>4</v>
       </c>
       <c r="E258" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F258" t="s">
         <v>9</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.4">
@@ -6663,19 +6664,19 @@
         <v>259</v>
       </c>
       <c r="B259" t="s">
+        <v>280</v>
+      </c>
+      <c r="C259" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" t="s">
         <v>281</v>
       </c>
-      <c r="C259" t="s">
-        <v>12</v>
-      </c>
-      <c r="E259" t="s">
-        <v>282</v>
-      </c>
       <c r="F259" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.4">
@@ -6683,19 +6684,19 @@
         <v>260</v>
       </c>
       <c r="B260" t="s">
+        <v>280</v>
+      </c>
+      <c r="C260" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260" t="s">
         <v>281</v>
-      </c>
-      <c r="C260" t="s">
-        <v>9</v>
-      </c>
-      <c r="E260" t="s">
-        <v>282</v>
       </c>
       <c r="F260" t="s">
         <v>11</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.4">
@@ -6703,19 +6704,19 @@
         <v>261</v>
       </c>
       <c r="B261" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C261" t="s">
         <v>7</v>
       </c>
       <c r="E261" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F261" t="s">
         <v>9</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.4">
@@ -6723,19 +6724,19 @@
         <v>262</v>
       </c>
       <c r="B262" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C262" t="s">
         <v>4</v>
       </c>
       <c r="E262" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F262" t="s">
         <v>9</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.4">
@@ -6743,19 +6744,19 @@
         <v>263</v>
       </c>
       <c r="B263" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C263" t="s">
         <v>4</v>
       </c>
       <c r="E263" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F263" t="s">
         <v>12</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.4">
@@ -6763,7 +6764,7 @@
         <v>264</v>
       </c>
       <c r="B264" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C264" t="s">
         <v>4</v>
@@ -6775,7 +6776,7 @@
         <v>19</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.4">
@@ -6783,7 +6784,7 @@
         <v>265</v>
       </c>
       <c r="B265" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C265" t="s">
         <v>12</v>
@@ -6795,7 +6796,7 @@
         <v>19</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.4">
@@ -6803,19 +6804,19 @@
         <v>266</v>
       </c>
       <c r="B266" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C266" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E266" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F266" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.4">
@@ -6823,22 +6824,22 @@
         <v>267</v>
       </c>
       <c r="B267" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C267" t="s">
         <v>12</v>
       </c>
       <c r="D267" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E267" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F267" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="20.25" x14ac:dyDescent="0.4">
@@ -6846,22 +6847,22 @@
         <v>268</v>
       </c>
       <c r="B268" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C268" t="s">
         <v>9</v>
       </c>
       <c r="D268" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E268" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F268" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I268" s="6"/>
     </row>
@@ -6870,16 +6871,16 @@
         <v>269</v>
       </c>
       <c r="B269" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C269" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E269" t="s">
+        <v>319</v>
+      </c>
+      <c r="H269" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="H269" s="4" t="s">
-        <v>321</v>
       </c>
     </row>
   </sheetData>
